--- a/survey_templates/044_customer_feedback_initiative_evaluation_form--survey_templates.xlsx
+++ b/survey_templates/044_customer_feedback_initiative_evaluation_form--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1106,8 +1106,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="31" customWidth="1" min="1" max="1"/>
-    <col width="45" customWidth="1" min="2" max="2"/>
-    <col width="45" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1135,12 +1135,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1152,12 +1152,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -1169,12 +1169,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_4,_'value':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 4, 'value': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1271,12 +1271,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'not_sure'}</t>
+          <t>not_sure</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Not sure'}</t>
+          <t>Not sure</t>
         </is>
       </c>
     </row>
@@ -1288,12 +1288,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'ceo'}</t>
+          <t>ceo</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'CEO'}</t>
+          <t>CEO</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'manager'}</t>
+          <t>manager</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Manager'}</t>
+          <t>Manager</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'team_member'}</t>
+          <t>team_member</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Team Member'}</t>
+          <t>Team Member</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'value':_'marketing'}</t>
+          <t>marketing</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'value': 'Marketing'}</t>
+          <t>Marketing</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'value':_'sales'}</t>
+          <t>sales</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'value': 'Sales'}</t>
+          <t>Sales</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'value':_'support'}</t>
+          <t>support</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'value': 'Support'}</t>
+          <t>Support</t>
         </is>
       </c>
     </row>
